--- a/catalogo_metas.xlsx
+++ b/catalogo_metas.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\702260697\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\702260697\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60F4936F-88EA-4FC6-B738-58C4E2DB2448}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68037BFB-5D8D-4B82-A762-C1E78FC7E17E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7A06F0CD-E95E-4A09-8794-A88688D2CABF}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2065" uniqueCount="438">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2065" uniqueCount="439">
   <si>
     <t>Delegacion</t>
   </si>
@@ -1353,6 +1353,9 @@
   </si>
   <si>
     <t>Duacari</t>
+  </si>
+  <si>
+    <t>Uruca/Mata Redonda</t>
   </si>
 </sst>
 </file>
@@ -2021,7 +2024,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>13</v>
       </c>
@@ -2035,7 +2038,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>13</v>
       </c>
@@ -2049,7 +2052,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>13</v>
       </c>
@@ -2065,44 +2068,44 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D24" s="2">
-        <v>383</v>
+        <v>311</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D25" s="2">
-        <v>244</v>
+        <v>71</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>16</v>
+        <v>438</v>
       </c>
       <c r="D26" s="2">
-        <v>55</v>
+        <v>272</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -2110,55 +2113,55 @@
         <v>17</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>17</v>
+        <v>438</v>
       </c>
       <c r="D27" s="2">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D28" s="2">
-        <v>71</v>
+        <v>383</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D29" s="2">
-        <v>272</v>
+        <v>244</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D30" s="2">
-        <v>89</v>
+        <v>55</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
